--- a/data/HCA_CBSA_profiles.xlsx
+++ b/data/HCA_CBSA_profiles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="132">
   <si>
     <t>Variable</t>
   </si>
@@ -46,55 +46,67 @@
     <t>CBSAs (n)</t>
   </si>
   <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
     <t>31</t>
   </si>
   <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>180</t>
+    <t>68</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>CBSA Type: Micropolitan</t>
   </si>
   <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
     <t>0.39</t>
   </si>
   <si>
     <t>0.00</t>
   </si>
   <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>0.67</t>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>CBSA Type: Metropolitan</t>
   </si>
   <si>
     <t>0.21</t>
   </si>
   <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>CBSA Type: Metropolitan</t>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>0.65</t>
   </si>
   <si>
     <t>0.61</t>
@@ -103,316 +115,301 @@
     <t>1.00</t>
   </si>
   <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
     <t>Number of Institutions in the Analytic Sample</t>
   </si>
   <si>
+    <t>1.00 (0.00)</t>
+  </si>
+  <si>
+    <t>1.17 (0.43)</t>
+  </si>
+  <si>
+    <t>2.27 (1.14)</t>
+  </si>
+  <si>
+    <t>2.24 (1.40)</t>
+  </si>
+  <si>
+    <t>3.56 (1.92)</t>
+  </si>
+  <si>
     <t>2.39 (1.17)</t>
   </si>
   <si>
-    <t>17.14 (16.06)</t>
-  </si>
-  <si>
-    <t>3.78 (2.76)</t>
-  </si>
-  <si>
-    <t>1.00 (0.00)</t>
-  </si>
-  <si>
-    <t>2.59 (0.95)</t>
-  </si>
-  <si>
-    <t>2.13 (1.43)</t>
-  </si>
-  <si>
-    <t>2.39 (1.25)</t>
+    <t>16.93 (15.87)</t>
+  </si>
+  <si>
+    <t>2.14 (1.25)</t>
   </si>
   <si>
     <t>Total Population (100,000s)</t>
   </si>
   <si>
+    <t>0.68 (0.60)</t>
+  </si>
+  <si>
+    <t>0.98 (1.06)</t>
+  </si>
+  <si>
+    <t>1.75 (1.88)</t>
+  </si>
+  <si>
+    <t>2.58 (2.71)</t>
+  </si>
+  <si>
+    <t>2.61 (2.68)</t>
+  </si>
+  <si>
     <t>2.56 (4.11)</t>
   </si>
   <si>
-    <t>29.04 (32.06)</t>
-  </si>
-  <si>
-    <t>3.72 (4.30)</t>
-  </si>
-  <si>
-    <t>0.85 (0.72)</t>
-  </si>
-  <si>
-    <t>0.95 (0.96)</t>
-  </si>
-  <si>
-    <t>3.36 (2.74)</t>
-  </si>
-  <si>
-    <t>1.46 (1.64)</t>
-  </si>
-  <si>
-    <t>2.07 (2.09)</t>
+    <t>28.52 (31.73)</t>
+  </si>
+  <si>
+    <t>1.47 (1.34)</t>
   </si>
   <si>
     <t>Population Density (Persons per Square Mile)</t>
   </si>
   <si>
+    <t>90.20 (77.49)</t>
+  </si>
+  <si>
+    <t>96.26 (101.44)</t>
+  </si>
+  <si>
+    <t>181.05 (201.40)</t>
+  </si>
+  <si>
+    <t>174.30 (216.78)</t>
+  </si>
+  <si>
+    <t>196.24 (147.45)</t>
+  </si>
+  <si>
     <t>150.61 (106.44)</t>
   </si>
   <si>
-    <t>677.64 (568.32)</t>
-  </si>
-  <si>
-    <t>195.83 (188.31)</t>
-  </si>
-  <si>
-    <t>86.54 (88.56)</t>
-  </si>
-  <si>
-    <t>90.96 (83.61)</t>
-  </si>
-  <si>
-    <t>185.61 (175.11)</t>
-  </si>
-  <si>
-    <t>140.96 (126.55)</t>
-  </si>
-  <si>
-    <t>239.09 (322.81)</t>
+    <t>673.61 (562.48)</t>
+  </si>
+  <si>
+    <t>127.06 (139.80)</t>
   </si>
   <si>
     <t>Population Aged 25+ with a Bachelor's Degree or Higher (%)</t>
   </si>
   <si>
+    <t>25.16 (7.31)</t>
+  </si>
+  <si>
+    <t>23.76 (7.85)</t>
+  </si>
+  <si>
+    <t>26.44 (7.94)</t>
+  </si>
+  <si>
+    <t>32.89 (8.99)</t>
+  </si>
+  <si>
+    <t>28.50 (7.42)</t>
+  </si>
+  <si>
     <t>26.88 (8.75)</t>
   </si>
   <si>
-    <t>38.79 (6.52)</t>
-  </si>
-  <si>
-    <t>29.79 (7.45)</t>
-  </si>
-  <si>
-    <t>23.20 (7.56)</t>
-  </si>
-  <si>
-    <t>33.61 (9.18)</t>
-  </si>
-  <si>
-    <t>31.78 (9.22)</t>
-  </si>
-  <si>
-    <t>26.67 (7.38)</t>
-  </si>
-  <si>
-    <t>28.61 (9.87)</t>
+    <t>38.79 (6.71)</t>
+  </si>
+  <si>
+    <t>27.64 (6.74)</t>
   </si>
   <si>
     <t>Median Household Income ($)</t>
   </si>
   <si>
+    <t>67798.93 (11514.61)</t>
+  </si>
+  <si>
+    <t>66425.01 (13207.86)</t>
+  </si>
+  <si>
+    <t>69222.42 (12100.72)</t>
+  </si>
+  <si>
+    <t>69182.85 (13705.35)</t>
+  </si>
+  <si>
+    <t>70557.56 (13227.96)</t>
+  </si>
+  <si>
     <t>62100.68 (12266.10)</t>
   </si>
   <si>
-    <t>87028.52 (17862.93)</t>
-  </si>
-  <si>
-    <t>68772.95 (11198.97)</t>
-  </si>
-  <si>
-    <t>66208.69 (13412.80)</t>
-  </si>
-  <si>
-    <t>64618.14 (13094.35)</t>
-  </si>
-  <si>
-    <t>71994.21 (13778.12)</t>
-  </si>
-  <si>
-    <t>68771.94 (11771.85)</t>
-  </si>
-  <si>
-    <t>69949.42 (13502.39)</t>
+    <t>86693.60 (17993.16)</t>
+  </si>
+  <si>
+    <t>66897.32 (9027.65)</t>
   </si>
   <si>
     <t>Families Below the Poverty Level (%)</t>
   </si>
   <si>
+    <t>9.01 (3.06)</t>
+  </si>
+  <si>
+    <t>10.55 (4.06)</t>
+  </si>
+  <si>
+    <t>9.37 (3.61)</t>
+  </si>
+  <si>
+    <t>9.78 (3.90)</t>
+  </si>
+  <si>
+    <t>9.16 (3.11)</t>
+  </si>
+  <si>
     <t>12.90 (4.82)</t>
   </si>
   <si>
-    <t>8.11 (2.05)</t>
-  </si>
-  <si>
-    <t>9.91 (3.15)</t>
-  </si>
-  <si>
-    <t>10.64 (4.02)</t>
-  </si>
-  <si>
-    <t>9.77 (4.14)</t>
-  </si>
-  <si>
-    <t>10.04 (4.36)</t>
-  </si>
-  <si>
-    <t>9.14 (3.03)</t>
-  </si>
-  <si>
-    <t>9.34 (3.62)</t>
+    <t>8.20 (2.11)</t>
+  </si>
+  <si>
+    <t>9.55 (3.21)</t>
   </si>
   <si>
     <t>Unemployment Rate (%)</t>
   </si>
   <si>
+    <t>2.53 (0.82)</t>
+  </si>
+  <si>
+    <t>2.91 (0.88)</t>
+  </si>
+  <si>
+    <t>2.72 (0.77)</t>
+  </si>
+  <si>
+    <t>3.01 (0.84)</t>
+  </si>
+  <si>
+    <t>2.74 (0.56)</t>
+  </si>
+  <si>
     <t>3.54 (1.08)</t>
   </si>
   <si>
-    <t>3.26 (0.57)</t>
-  </si>
-  <si>
-    <t>2.73 (0.71)</t>
-  </si>
-  <si>
-    <t>2.91 (0.91)</t>
-  </si>
-  <si>
-    <t>2.96 (0.88)</t>
-  </si>
-  <si>
-    <t>3.11 (0.85)</t>
-  </si>
-  <si>
-    <t>2.67 (0.72)</t>
-  </si>
-  <si>
-    <t>2.77 (0.78)</t>
+    <t>3.27 (0.57)</t>
+  </si>
+  <si>
+    <t>2.56 (0.72)</t>
   </si>
   <si>
     <t>Non-Hispanic White Population (%)</t>
   </si>
   <si>
+    <t>82.35 (11.07)</t>
+  </si>
+  <si>
+    <t>69.38 (19.23)</t>
+  </si>
+  <si>
+    <t>75.55 (16.14)</t>
+  </si>
+  <si>
+    <t>68.67 (18.78)</t>
+  </si>
+  <si>
+    <t>75.66 (13.24)</t>
+  </si>
+  <si>
     <t>51.26 (16.59)</t>
   </si>
   <si>
-    <t>57.57 (16.62)</t>
-  </si>
-  <si>
-    <t>69.57 (15.80)</t>
-  </si>
-  <si>
-    <t>68.98 (19.32)</t>
-  </si>
-  <si>
-    <t>73.50 (15.33)</t>
-  </si>
-  <si>
-    <t>63.39 (22.15)</t>
-  </si>
-  <si>
-    <t>78.72 (12.73)</t>
-  </si>
-  <si>
-    <t>74.43 (16.45)</t>
+    <t>57.17 (16.40)</t>
+  </si>
+  <si>
+    <t>74.22 (16.30)</t>
   </si>
   <si>
     <t>Non-Hispanic Black Population (%)</t>
   </si>
   <si>
+    <t>4.33 (6.90)</t>
+  </si>
+  <si>
+    <t>7.06 (10.91)</t>
+  </si>
+  <si>
+    <t>7.43 (9.21)</t>
+  </si>
+  <si>
+    <t>8.58 (10.81)</t>
+  </si>
+  <si>
+    <t>9.45 (11.63)</t>
+  </si>
+  <si>
     <t>26.10 (20.53)</t>
   </si>
   <si>
-    <t>12.91 (9.70)</t>
-  </si>
-  <si>
-    <t>15.27 (14.60)</t>
-  </si>
-  <si>
-    <t>7.04 (11.27)</t>
-  </si>
-  <si>
-    <t>7.45 (11.79)</t>
-  </si>
-  <si>
-    <t>7.39 (8.54)</t>
-  </si>
-  <si>
-    <t>7.00 (9.65)</t>
-  </si>
-  <si>
-    <t>7.75 (9.36)</t>
+    <t>13.75 (10.42)</t>
+  </si>
+  <si>
+    <t>11.74 (14.48)</t>
   </si>
   <si>
     <t>Hispanic or Latino Population (%)</t>
   </si>
   <si>
+    <t>7.19 (6.27)</t>
+  </si>
+  <si>
+    <t>15.33 (16.54)</t>
+  </si>
+  <si>
+    <t>10.66 (12.07)</t>
+  </si>
+  <si>
+    <t>14.55 (18.22)</t>
+  </si>
+  <si>
+    <t>7.61 (6.47)</t>
+  </si>
+  <si>
     <t>14.18 (16.98)</t>
   </si>
   <si>
-    <t>17.31 (13.59)</t>
-  </si>
-  <si>
-    <t>8.20 (6.87)</t>
-  </si>
-  <si>
-    <t>16.23 (17.31)</t>
-  </si>
-  <si>
-    <t>10.61 (12.09)</t>
-  </si>
-  <si>
-    <t>19.71 (23.03)</t>
-  </si>
-  <si>
-    <t>7.54 (6.31)</t>
-  </si>
-  <si>
-    <t>11.16 (12.51)</t>
+    <t>16.98 (13.54)</t>
+  </si>
+  <si>
+    <t>7.43 (8.22)</t>
   </si>
   <si>
     <t>Non-Hispanic Asian Population (%)</t>
   </si>
   <si>
+    <t>0.91 (0.58)</t>
+  </si>
+  <si>
+    <t>1.56 (3.14)</t>
+  </si>
+  <si>
+    <t>1.82 (2.71)</t>
+  </si>
+  <si>
+    <t>2.50 (1.89)</t>
+  </si>
+  <si>
+    <t>1.87 (1.65)</t>
+  </si>
+  <si>
     <t>2.66 (3.89)</t>
   </si>
   <si>
-    <t>6.58 (7.45)</t>
-  </si>
-  <si>
-    <t>1.97 (1.35)</t>
-  </si>
-  <si>
-    <t>1.51 (3.22)</t>
-  </si>
-  <si>
-    <t>2.11 (1.62)</t>
-  </si>
-  <si>
-    <t>2.57 (1.89)</t>
-  </si>
-  <si>
-    <t>1.43 (1.62)</t>
-  </si>
-  <si>
-    <t>2.37 (3.08)</t>
+    <t>6.51 (7.36)</t>
+  </si>
+  <si>
+    <t>1.36 (0.97)</t>
   </si>
 </sst>
 </file>
@@ -813,24 +810,24 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -862,335 +859,335 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
         <v>31</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>38</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>39</v>
       </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>40</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>41</v>
-      </c>
-      <c r="I5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>45</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>46</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>48</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>49</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>50</v>
-      </c>
-      <c r="I6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>53</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>55</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>56</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>57</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>58</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>59</v>
-      </c>
-      <c r="I7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>62</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>63</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>64</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>65</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>66</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>67</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>68</v>
-      </c>
-      <c r="I8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>71</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>72</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>73</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>74</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>75</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>76</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>77</v>
-      </c>
-      <c r="I9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>80</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>81</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>82</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>83</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>84</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>85</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>86</v>
-      </c>
-      <c r="I10" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
         <v>88</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>89</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>90</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>91</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>92</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>93</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>94</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>95</v>
-      </c>
-      <c r="I11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
         <v>97</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>98</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>99</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>100</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>101</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>102</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>103</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>104</v>
-      </c>
-      <c r="I12" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" t="s">
         <v>106</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>107</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>108</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>109</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>110</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>111</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>112</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>113</v>
-      </c>
-      <c r="I13" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
         <v>115</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>116</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>117</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>118</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>119</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>120</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>121</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>122</v>
-      </c>
-      <c r="I14" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" t="s">
         <v>124</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>125</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>126</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>127</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>128</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>129</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>130</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>131</v>
-      </c>
-      <c r="I15" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
